--- a/timetable_backend/courses_calculated.xlsx
+++ b/timetable_backend/courses_calculated.xlsx
@@ -431,17 +431,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
